--- a/indicator_groups_review_UPDATED.xlsx
+++ b/indicator_groups_review_UPDATED.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kasim\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3301B314-B8FD-42D7-B24A-5A58F00B02BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9851965E-F7EB-4A48-87DC-E34A54218045}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-135" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,14 +16,14 @@
     <sheet name="Indicator Groups Review" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Indicator Groups Review'!$A$1:$M$71</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Indicator Groups Review'!$A$1:$L$71</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="728" uniqueCount="395">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="717" uniqueCount="394">
   <si>
     <t>id</t>
   </si>
@@ -1070,9 +1070,6 @@
   </si>
   <si>
     <t>Keep</t>
-  </si>
-  <si>
-    <t>new_naturally_leading</t>
   </si>
   <si>
     <t>AS_CN_G3</t>
@@ -1305,7 +1302,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1322,26 +1319,16 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -1645,7 +1632,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L71"/>
+  <dimension ref="A1:K71"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -1653,15 +1640,13 @@
     <col min="3" max="3" width="55" customWidth="1"/>
     <col min="4" max="4" width="70" customWidth="1"/>
     <col min="5" max="5" width="28" customWidth="1"/>
-    <col min="6" max="6" width="18" customWidth="1"/>
-    <col min="7" max="7" width="18" style="7" customWidth="1"/>
+    <col min="6" max="7" width="18" customWidth="1"/>
     <col min="8" max="8" width="15.7109375" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="28.85546875" customWidth="1"/>
     <col min="10" max="10" width="31.42578125" customWidth="1"/>
-    <col min="11" max="11" width="21.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1692,14 +1677,11 @@
       <c r="J1" s="5" t="s">
         <v>294</v>
       </c>
-      <c r="K1" s="1" t="s">
-        <v>349</v>
-      </c>
-      <c r="L1" s="5" t="s">
+      <c r="K1" s="5" t="s">
         <v>306</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>206</v>
       </c>
@@ -1728,12 +1710,11 @@
       <c r="J2" s="2" t="s">
         <v>207</v>
       </c>
-      <c r="K2" s="4"/>
-      <c r="L2" s="2" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="K2" s="2" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>211</v>
       </c>
@@ -1762,12 +1743,11 @@
       <c r="J3" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="K3" s="4"/>
-      <c r="L3" s="2" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" ht="63.75" x14ac:dyDescent="0.25">
+      <c r="K3" s="2" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>219</v>
       </c>
@@ -1796,12 +1776,11 @@
       <c r="J4" s="2" t="s">
         <v>220</v>
       </c>
-      <c r="K4" s="4"/>
-      <c r="L4" s="2" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" ht="51" x14ac:dyDescent="0.25">
+      <c r="K4" s="2" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="51" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>223</v>
       </c>
@@ -1830,12 +1809,11 @@
       <c r="J5" s="2" t="s">
         <v>224</v>
       </c>
-      <c r="K5" s="4"/>
-      <c r="L5" s="2" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" ht="51" x14ac:dyDescent="0.25">
+      <c r="K5" s="2" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="51" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>268</v>
       </c>
@@ -1866,14 +1844,11 @@
       <c r="J6" s="2" t="s">
         <v>269</v>
       </c>
-      <c r="K6" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="L6" s="2" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="K6" s="2" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>215</v>
       </c>
@@ -1902,12 +1877,11 @@
       <c r="J7" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="K7" s="4"/>
-      <c r="L7" s="2" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" ht="51" x14ac:dyDescent="0.25">
+      <c r="K7" s="2" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="51" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>227</v>
       </c>
@@ -1936,12 +1910,11 @@
       <c r="J8" s="2" t="s">
         <v>345</v>
       </c>
-      <c r="K8" s="4"/>
-      <c r="L8" s="2" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" ht="63.75" x14ac:dyDescent="0.25">
+      <c r="K8" s="2" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>264</v>
       </c>
@@ -1972,14 +1945,11 @@
       <c r="J9" s="2" t="s">
         <v>265</v>
       </c>
-      <c r="K9" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="L9" s="2" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="K9" s="2" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>182</v>
       </c>
@@ -2008,12 +1978,11 @@
       <c r="J10" s="2" t="s">
         <v>341</v>
       </c>
-      <c r="K10" s="4"/>
-      <c r="L10" s="2" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="K10" s="2" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>202</v>
       </c>
@@ -2042,12 +2011,11 @@
       <c r="J11" s="2" t="s">
         <v>203</v>
       </c>
-      <c r="K11" s="4"/>
-      <c r="L11" s="2" t="s">
+      <c r="K11" s="2" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="12" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>165</v>
       </c>
@@ -2076,12 +2044,11 @@
       <c r="J12" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="K12" s="4"/>
-      <c r="L12" s="2" t="s">
+      <c r="K12" s="2" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="13" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>174</v>
       </c>
@@ -2110,12 +2077,11 @@
       <c r="J13" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="K13" s="4"/>
-      <c r="L13" s="2" t="s">
+      <c r="K13" s="2" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="14" spans="1:12" ht="51" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" ht="51" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>178</v>
       </c>
@@ -2141,15 +2107,14 @@
       <c r="I14" s="6" t="s">
         <v>301</v>
       </c>
-      <c r="J14" s="13" t="s">
+      <c r="J14" s="6" t="s">
         <v>179</v>
       </c>
-      <c r="K14" s="4"/>
-      <c r="L14" s="2" t="s">
+      <c r="K14" s="2" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="15" spans="1:12" ht="51" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" ht="51" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>194</v>
       </c>
@@ -2178,12 +2143,11 @@
       <c r="J15" s="6" t="s">
         <v>344</v>
       </c>
-      <c r="K15" s="4"/>
-      <c r="L15" s="2" t="s">
+      <c r="K15" s="2" t="s">
         <v>198</v>
       </c>
     </row>
-    <row r="16" spans="1:12" ht="63.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>231</v>
       </c>
@@ -2212,12 +2176,11 @@
       <c r="J16" s="2" t="s">
         <v>232</v>
       </c>
-      <c r="K16" s="4"/>
-      <c r="L16" s="2" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="K16" s="2" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>102</v>
       </c>
@@ -2243,15 +2206,14 @@
       <c r="I17" s="6" t="s">
         <v>310</v>
       </c>
-      <c r="J17" s="13" t="s">
+      <c r="J17" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="K17" s="4"/>
-      <c r="L17" s="2" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="K17" s="2" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>107</v>
       </c>
@@ -2277,15 +2239,14 @@
       <c r="I18" s="6" t="s">
         <v>310</v>
       </c>
-      <c r="J18" s="13" t="s">
+      <c r="J18" s="6" t="s">
         <v>108</v>
       </c>
-      <c r="K18" s="4"/>
-      <c r="L18" s="2" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="K18" s="2" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>244</v>
       </c>
@@ -2314,12 +2275,11 @@
       <c r="J19" s="2" t="s">
         <v>245</v>
       </c>
-      <c r="K19" s="4"/>
-      <c r="L19" s="2" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="K19" s="2" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>239</v>
       </c>
@@ -2342,18 +2302,17 @@
       <c r="H20" s="6" t="s">
         <v>314</v>
       </c>
-      <c r="I20" s="10" t="s">
+      <c r="I20" s="8" t="s">
         <v>328</v>
       </c>
-      <c r="J20" s="9" t="s">
+      <c r="J20" s="8" t="s">
         <v>240</v>
       </c>
-      <c r="K20" s="4"/>
-      <c r="L20" s="2" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12" ht="51" x14ac:dyDescent="0.25">
+      <c r="K20" s="2" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" ht="51" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>284</v>
       </c>
@@ -2376,18 +2335,17 @@
       <c r="H21" s="6" t="s">
         <v>314</v>
       </c>
-      <c r="I21" s="8" t="s">
+      <c r="I21" s="7" t="s">
         <v>332</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>285</v>
       </c>
-      <c r="K21" s="4"/>
-      <c r="L21" s="2" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12" ht="63.75" x14ac:dyDescent="0.25">
+      <c r="K21" s="2" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>235</v>
       </c>
@@ -2410,18 +2368,17 @@
       <c r="H22" s="6" t="s">
         <v>314</v>
       </c>
-      <c r="I22" s="8" t="s">
+      <c r="I22" s="7" t="s">
         <v>327</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>236</v>
       </c>
-      <c r="K22" s="4"/>
-      <c r="L22" s="2" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12" ht="63.75" x14ac:dyDescent="0.25">
+      <c r="K22" s="2" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>288</v>
       </c>
@@ -2444,18 +2401,17 @@
       <c r="H23" s="6" t="s">
         <v>314</v>
       </c>
-      <c r="I23" s="8" t="s">
+      <c r="I23" s="7" t="s">
         <v>71</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>289</v>
       </c>
-      <c r="K23" s="4"/>
-      <c r="L23" s="2" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="24" spans="1:12" ht="63.75" x14ac:dyDescent="0.25">
+      <c r="K23" s="2" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>252</v>
       </c>
@@ -2480,20 +2436,17 @@
       <c r="H24" s="6" t="s">
         <v>314</v>
       </c>
-      <c r="I24" s="8" t="s">
+      <c r="I24" s="7" t="s">
         <v>330</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="K24" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="L24" s="2" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="25" spans="1:12" ht="51" x14ac:dyDescent="0.25">
+      <c r="K24" s="2" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" ht="51" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>256</v>
       </c>
@@ -2518,20 +2471,17 @@
       <c r="H25" s="6" t="s">
         <v>300</v>
       </c>
-      <c r="I25" s="8" t="s">
+      <c r="I25" s="7" t="s">
         <v>331</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>346</v>
       </c>
-      <c r="K25" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="L25" s="2" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="26" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="K25" s="2" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>261</v>
       </c>
@@ -2556,20 +2506,17 @@
       <c r="H26" s="6" t="s">
         <v>300</v>
       </c>
-      <c r="I26" s="8" t="s">
+      <c r="I26" s="7" t="s">
         <v>331</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>347</v>
       </c>
-      <c r="K26" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="L26" s="2" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="27" spans="1:12" ht="63.75" x14ac:dyDescent="0.25">
+      <c r="K26" s="2" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>272</v>
       </c>
@@ -2594,20 +2541,17 @@
       <c r="H27" s="6" t="s">
         <v>300</v>
       </c>
-      <c r="I27" s="8" t="s">
+      <c r="I27" s="7" t="s">
         <v>331</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>273</v>
       </c>
-      <c r="K27" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="L27" s="2" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="28" spans="1:12" ht="63.75" x14ac:dyDescent="0.25">
+      <c r="K27" s="2" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>280</v>
       </c>
@@ -2630,18 +2574,17 @@
       <c r="H28" s="6" t="s">
         <v>300</v>
       </c>
-      <c r="I28" s="8" t="s">
+      <c r="I28" s="7" t="s">
         <v>310</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>281</v>
       </c>
-      <c r="K28" s="4"/>
-      <c r="L28" s="2" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="29" spans="1:12" ht="51" x14ac:dyDescent="0.25">
+      <c r="K28" s="2" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" ht="51" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>276</v>
       </c>
@@ -2664,18 +2607,17 @@
       <c r="H29" s="6" t="s">
         <v>300</v>
       </c>
-      <c r="I29" s="8" t="s">
+      <c r="I29" s="7" t="s">
         <v>310</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>277</v>
       </c>
-      <c r="K29" s="4"/>
-      <c r="L29" s="2" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="30" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="K29" s="2" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
         <v>52</v>
       </c>
@@ -2698,18 +2640,17 @@
       <c r="H30" s="6" t="s">
         <v>300</v>
       </c>
-      <c r="I30" s="8" t="s">
+      <c r="I30" s="7" t="s">
         <v>309</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="K30" s="4"/>
-      <c r="L30" s="2" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="31" spans="1:12" ht="51" x14ac:dyDescent="0.25">
+      <c r="K30" s="2" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" ht="51" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>248</v>
       </c>
@@ -2732,18 +2673,17 @@
       <c r="H31" s="6" t="s">
         <v>299</v>
       </c>
-      <c r="I31" s="8" t="s">
+      <c r="I31" s="7" t="s">
         <v>301</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>249</v>
       </c>
-      <c r="K31" s="4"/>
-      <c r="L31" s="2" t="s">
+      <c r="K31" s="2" t="s">
         <v>248</v>
       </c>
     </row>
-    <row r="32" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>198</v>
       </c>
@@ -2766,18 +2706,17 @@
       <c r="H32" s="6" t="s">
         <v>297</v>
       </c>
-      <c r="I32" s="8" t="s">
+      <c r="I32" s="7" t="s">
         <v>305</v>
       </c>
       <c r="J32" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="K32" s="4"/>
-      <c r="L32" s="2" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="33" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="K32" s="2" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
         <v>170</v>
       </c>
@@ -2800,18 +2739,17 @@
       <c r="H33" s="6" t="s">
         <v>297</v>
       </c>
-      <c r="I33" s="8" t="s">
+      <c r="I33" s="7" t="s">
         <v>301</v>
       </c>
       <c r="J33" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="K33" s="4"/>
-      <c r="L33" s="2" t="s">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="34" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="K33" s="2" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
         <v>190</v>
       </c>
@@ -2834,18 +2772,17 @@
       <c r="H34" s="6" t="s">
         <v>297</v>
       </c>
-      <c r="I34" s="8" t="s">
+      <c r="I34" s="7" t="s">
         <v>308</v>
       </c>
-      <c r="J34" s="12" t="s">
+      <c r="J34" s="2" t="s">
         <v>343</v>
       </c>
-      <c r="K34" s="4"/>
-      <c r="L34" s="2" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="35" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="K34" s="2" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
         <v>186</v>
       </c>
@@ -2868,18 +2805,17 @@
       <c r="H35" s="6" t="s">
         <v>297</v>
       </c>
-      <c r="I35" s="8" t="s">
+      <c r="I35" s="7" t="s">
         <v>307</v>
       </c>
-      <c r="J35" s="12" t="s">
+      <c r="J35" s="2" t="s">
         <v>342</v>
       </c>
-      <c r="K35" s="4"/>
-      <c r="L35" s="2" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="36" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="K35" s="2" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
         <v>82</v>
       </c>
@@ -2902,18 +2838,17 @@
       <c r="H36" s="6" t="s">
         <v>295</v>
       </c>
-      <c r="I36" s="8" t="s">
+      <c r="I36" s="7" t="s">
         <v>305</v>
       </c>
       <c r="J36" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="K36" s="4"/>
-      <c r="L36" s="2" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="37" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="K36" s="2" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
         <v>48</v>
       </c>
@@ -2936,18 +2871,17 @@
       <c r="H37" s="6" t="s">
         <v>295</v>
       </c>
-      <c r="I37" s="8" t="s">
+      <c r="I37" s="7" t="s">
         <v>305</v>
       </c>
       <c r="J37" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="K37" s="4"/>
-      <c r="L37" s="2" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="38" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="K37" s="2" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
         <v>56</v>
       </c>
@@ -2970,18 +2904,17 @@
       <c r="H38" s="6" t="s">
         <v>295</v>
       </c>
-      <c r="I38" s="8" t="s">
+      <c r="I38" s="7" t="s">
         <v>305</v>
       </c>
-      <c r="J38" s="12" t="s">
+      <c r="J38" s="2" t="s">
         <v>335</v>
       </c>
-      <c r="K38" s="4"/>
-      <c r="L38" s="2" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="39" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="K38" s="2" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
         <v>60</v>
       </c>
@@ -3004,18 +2937,17 @@
       <c r="H39" s="6" t="s">
         <v>295</v>
       </c>
-      <c r="I39" s="8" t="s">
+      <c r="I39" s="7" t="s">
         <v>305</v>
       </c>
-      <c r="J39" s="12" t="s">
+      <c r="J39" s="2" t="s">
         <v>336</v>
       </c>
-      <c r="K39" s="4"/>
-      <c r="L39" s="2" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="40" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="K39" s="2" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
         <v>74</v>
       </c>
@@ -3038,18 +2970,17 @@
       <c r="H40" s="6" t="s">
         <v>295</v>
       </c>
-      <c r="I40" s="8" t="s">
+      <c r="I40" s="7" t="s">
         <v>310</v>
       </c>
       <c r="J40" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="K40" s="4"/>
-      <c r="L40" s="2" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="41" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="K40" s="2" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
         <v>19</v>
       </c>
@@ -3078,12 +3009,11 @@
       <c r="J41" s="2" t="s">
         <v>333</v>
       </c>
-      <c r="K41" s="4"/>
-      <c r="L41" s="2" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="42" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="K41" s="2" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
         <v>23</v>
       </c>
@@ -3112,12 +3042,11 @@
       <c r="J42" s="2" t="s">
         <v>334</v>
       </c>
-      <c r="K42" s="4"/>
-      <c r="L42" s="2" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="43" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="K42" s="2" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
         <v>27</v>
       </c>
@@ -3146,12 +3075,11 @@
       <c r="J43" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="K43" s="4"/>
-      <c r="L43" s="2" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="44" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="K43" s="2" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
         <v>31</v>
       </c>
@@ -3180,12 +3108,11 @@
       <c r="J44" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="K44" s="4"/>
-      <c r="L44" s="2" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="45" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="K44" s="2" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
         <v>6</v>
       </c>
@@ -3208,18 +3135,17 @@
       <c r="H45" s="6" t="s">
         <v>295</v>
       </c>
-      <c r="I45" s="8" t="s">
+      <c r="I45" s="7" t="s">
         <v>301</v>
       </c>
       <c r="J45" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="K45" s="4"/>
-      <c r="L45" s="2" t="s">
+      <c r="K45" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="46" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:11" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
         <v>11</v>
       </c>
@@ -3245,15 +3171,14 @@
       <c r="I46" s="6" t="s">
         <v>301</v>
       </c>
-      <c r="J46" s="13" t="s">
+      <c r="J46" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="K46" s="4"/>
-      <c r="L46" s="2" t="s">
+      <c r="K46" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="47" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
         <v>15</v>
       </c>
@@ -3276,18 +3201,17 @@
       <c r="H47" s="6" t="s">
         <v>295</v>
       </c>
-      <c r="I47" s="8" t="s">
+      <c r="I47" s="7" t="s">
         <v>301</v>
       </c>
-      <c r="J47" s="13" t="s">
+      <c r="J47" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="K47" s="4"/>
-      <c r="L47" s="2" t="s">
+      <c r="K47" s="2" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="48" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:11" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
         <v>35</v>
       </c>
@@ -3310,18 +3234,17 @@
       <c r="H48" s="6" t="s">
         <v>295</v>
       </c>
-      <c r="I48" s="8" t="s">
+      <c r="I48" s="7" t="s">
         <v>301</v>
       </c>
-      <c r="J48" s="13" t="s">
+      <c r="J48" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="K48" s="4"/>
-      <c r="L48" s="2" t="s">
+      <c r="K48" s="2" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="49" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:11" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
         <v>39</v>
       </c>
@@ -3344,18 +3267,17 @@
       <c r="H49" s="6" t="s">
         <v>295</v>
       </c>
-      <c r="I49" s="8" t="s">
+      <c r="I49" s="7" t="s">
         <v>301</v>
       </c>
       <c r="J49" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="K49" s="4"/>
-      <c r="L49" s="2" t="s">
+      <c r="K49" s="2" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="50" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
         <v>149</v>
       </c>
@@ -3384,12 +3306,11 @@
       <c r="J50" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="K50" s="4"/>
-      <c r="L50" s="2" t="s">
+      <c r="K50" s="2" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="51" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
         <v>153</v>
       </c>
@@ -3414,20 +3335,17 @@
       <c r="H51" s="6" t="s">
         <v>295</v>
       </c>
-      <c r="I51" s="8" t="s">
+      <c r="I51" s="7" t="s">
         <v>319</v>
       </c>
       <c r="J51" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="K51" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="L51" s="2" t="s">
+      <c r="K51" s="2" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="52" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
         <v>137</v>
       </c>
@@ -3450,18 +3368,17 @@
       <c r="H52" s="6" t="s">
         <v>295</v>
       </c>
-      <c r="I52" s="8" t="s">
+      <c r="I52" s="7" t="s">
         <v>319</v>
       </c>
       <c r="J52" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="K52" s="4"/>
-      <c r="L52" s="2" t="s">
+      <c r="K52" s="2" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="53" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
         <v>141</v>
       </c>
@@ -3484,18 +3401,17 @@
       <c r="H53" s="6" t="s">
         <v>295</v>
       </c>
-      <c r="I53" s="8" t="s">
+      <c r="I53" s="7" t="s">
         <v>319</v>
       </c>
       <c r="J53" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="K53" s="4"/>
-      <c r="L53" s="2" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="54" spans="1:12" ht="63.75" x14ac:dyDescent="0.25">
+      <c r="K53" s="2" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
         <v>145</v>
       </c>
@@ -3520,20 +3436,17 @@
       <c r="H54" s="6" t="s">
         <v>295</v>
       </c>
-      <c r="I54" s="8" t="s">
+      <c r="I54" s="7" t="s">
         <v>319</v>
       </c>
       <c r="J54" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="K54" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="L54" s="2" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="55" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="K54" s="2" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="55" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
         <v>131</v>
       </c>
@@ -3558,20 +3471,17 @@
       <c r="H55" s="6" t="s">
         <v>295</v>
       </c>
-      <c r="I55" s="8" t="s">
+      <c r="I55" s="7" t="s">
         <v>319</v>
       </c>
       <c r="J55" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="K55" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="L55" s="2" t="s">
+      <c r="K55" s="2" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="56" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:11" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
         <v>157</v>
       </c>
@@ -3594,18 +3504,17 @@
       <c r="H56" s="6" t="s">
         <v>295</v>
       </c>
-      <c r="I56" s="8" t="s">
+      <c r="I56" s="7" t="s">
         <v>319</v>
       </c>
       <c r="J56" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="K56" s="4"/>
-      <c r="L56" s="2" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="57" spans="1:12" ht="63.75" x14ac:dyDescent="0.25">
+      <c r="K56" s="2" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="57" spans="1:11" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
         <v>161</v>
       </c>
@@ -3630,20 +3539,17 @@
       <c r="H57" s="6" t="s">
         <v>295</v>
       </c>
-      <c r="I57" s="8" t="s">
+      <c r="I57" s="7" t="s">
         <v>320</v>
       </c>
       <c r="J57" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="K57" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="L57" s="2" t="s">
+      <c r="K57" s="2" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="58" spans="1:12" ht="51" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:11" ht="51" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
         <v>123</v>
       </c>
@@ -3666,18 +3572,17 @@
       <c r="H58" s="6" t="s">
         <v>295</v>
       </c>
-      <c r="I58" s="8" t="s">
+      <c r="I58" s="7" t="s">
         <v>317</v>
       </c>
       <c r="J58" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="K58" s="4"/>
-      <c r="L58" s="2" t="s">
+      <c r="K58" s="2" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="59" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:11" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
         <v>115</v>
       </c>
@@ -3700,18 +3605,17 @@
       <c r="H59" s="6" t="s">
         <v>295</v>
       </c>
-      <c r="I59" s="8" t="s">
+      <c r="I59" s="7" t="s">
         <v>316</v>
       </c>
       <c r="J59" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="K59" s="4"/>
-      <c r="L59" s="2" t="s">
+      <c r="K59" s="2" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="60" spans="1:12" ht="51" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:11" ht="51" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
         <v>119</v>
       </c>
@@ -3734,18 +3638,17 @@
       <c r="H60" s="6" t="s">
         <v>295</v>
       </c>
-      <c r="I60" s="8" t="s">
+      <c r="I60" s="7" t="s">
         <v>316</v>
       </c>
       <c r="J60" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="K60" s="4"/>
-      <c r="L60" s="2" t="s">
+      <c r="K60" s="2" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="61" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
         <v>111</v>
       </c>
@@ -3768,18 +3671,17 @@
       <c r="H61" s="6" t="s">
         <v>295</v>
       </c>
-      <c r="I61" s="8" t="s">
+      <c r="I61" s="7" t="s">
         <v>315</v>
       </c>
       <c r="J61" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="K61" s="4"/>
-      <c r="L61" s="2" t="s">
+      <c r="K61" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="62" spans="1:12" ht="63.75" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:11" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
         <v>127</v>
       </c>
@@ -3802,18 +3704,17 @@
       <c r="H62" s="6" t="s">
         <v>295</v>
       </c>
-      <c r="I62" s="8" t="s">
+      <c r="I62" s="7" t="s">
         <v>318</v>
       </c>
       <c r="J62" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="K62" s="4"/>
-      <c r="L62" s="2" t="s">
+      <c r="K62" s="2" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="63" spans="1:12" ht="51" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:11" ht="51" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
         <v>86</v>
       </c>
@@ -3836,18 +3737,17 @@
       <c r="H63" s="6" t="s">
         <v>295</v>
       </c>
-      <c r="I63" s="8" t="s">
+      <c r="I63" s="7" t="s">
         <v>304</v>
       </c>
       <c r="J63" s="2" t="s">
         <v>339</v>
       </c>
-      <c r="K63" s="4"/>
-      <c r="L63" s="2" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="64" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="K63" s="2" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="64" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
         <v>98</v>
       </c>
@@ -3870,18 +3770,17 @@
       <c r="H64" s="6" t="s">
         <v>295</v>
       </c>
-      <c r="I64" s="8" t="s">
+      <c r="I64" s="7" t="s">
         <v>304</v>
       </c>
       <c r="J64" s="2" t="s">
         <v>340</v>
       </c>
-      <c r="K64" s="4"/>
-      <c r="L64" s="2" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="65" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="K64" s="2" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="65" spans="1:11" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
         <v>43</v>
       </c>
@@ -3904,18 +3803,17 @@
       <c r="H65" s="6" t="s">
         <v>295</v>
       </c>
-      <c r="I65" s="8" t="s">
+      <c r="I65" s="7" t="s">
         <v>308</v>
       </c>
       <c r="J65" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="K65" s="4"/>
-      <c r="L65" s="2" t="s">
+      <c r="K65" s="2" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="66" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:11" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
         <v>63</v>
       </c>
@@ -3938,18 +3836,17 @@
       <c r="H66" s="6" t="s">
         <v>295</v>
       </c>
-      <c r="I66" s="8" t="s">
+      <c r="I66" s="7" t="s">
         <v>308</v>
       </c>
       <c r="J66" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="K66" s="4"/>
-      <c r="L66" s="2" t="s">
+      <c r="K66" s="2" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="67" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
         <v>66</v>
       </c>
@@ -3972,18 +3869,17 @@
       <c r="H67" s="6" t="s">
         <v>295</v>
       </c>
-      <c r="I67" s="8" t="s">
+      <c r="I67" s="7" t="s">
         <v>308</v>
       </c>
-      <c r="J67" s="12" t="s">
+      <c r="J67" s="2" t="s">
         <v>337</v>
       </c>
-      <c r="K67" s="4"/>
-      <c r="L67" s="2" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="68" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="K67" s="2" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="68" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
         <v>70</v>
       </c>
@@ -4006,18 +3902,17 @@
       <c r="H68" s="6" t="s">
         <v>295</v>
       </c>
-      <c r="I68" s="8" t="s">
+      <c r="I68" s="7" t="s">
         <v>307</v>
       </c>
-      <c r="J68" s="12" t="s">
+      <c r="J68" s="2" t="s">
         <v>338</v>
       </c>
-      <c r="K68" s="4"/>
-      <c r="L68" s="2" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="69" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="K68" s="2" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="69" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
         <v>90</v>
       </c>
@@ -4040,18 +3935,17 @@
       <c r="H69" s="6" t="s">
         <v>295</v>
       </c>
-      <c r="I69" s="8" t="s">
+      <c r="I69" s="7" t="s">
         <v>313</v>
       </c>
       <c r="J69" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="K69" s="4"/>
-      <c r="L69" s="2" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="70" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="K69" s="2" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="70" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
         <v>94</v>
       </c>
@@ -4074,18 +3968,17 @@
       <c r="H70" s="6" t="s">
         <v>295</v>
       </c>
-      <c r="I70" s="8" t="s">
+      <c r="I70" s="7" t="s">
         <v>313</v>
       </c>
       <c r="J70" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="K70" s="4"/>
-      <c r="L70" s="2" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="71" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="K70" s="2" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="71" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
         <v>78</v>
       </c>
@@ -4106,14 +3999,13 @@
         <v>311</v>
       </c>
       <c r="H71" s="6"/>
-      <c r="I71" s="11"/>
-      <c r="J71" s="14"/>
-      <c r="K71" s="4"/>
-      <c r="L71" s="2"/>
+      <c r="I71" s="9"/>
+      <c r="J71" s="10"/>
+      <c r="K71" s="2"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M71" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L70">
+  <autoFilter ref="A1:L71" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K70">
     <sortCondition ref="H2:H70"/>
     <sortCondition ref="I2:I70"/>
     <sortCondition ref="A2:A70"/>
